--- a/hira_material_automation/output/monthly/202601_202606__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:24:28</t>
+          <t>2026-06-14T22:17:46</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d86074371b8f743af4a6944fe8bcc7f06d51167a29c729690c2888e67366abc9</t>
+          <t>df163be77c36125e7c594b84bfc6ce4d8befdf45d69946b4660599e307d3a09b</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:46</t>
+          <t>2026-06-24T22:22:32</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>df163be77c36125e7c594b84bfc6ce4d8befdf45d69946b4660599e307d3a09b</t>
+          <t>0f0f86b8bc1355b6b69d8463e11f4ae345523459be557db78aa59607b52b31d6</t>
         </is>
       </c>
     </row>
